--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DBIMA</t>
+          <t>DITMG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Datadrivet ledarskap eller Ledarskapets ekonomi` (7,5 hp); rad: - Datadrivet ledarskap eller Ledarskapets ekonomi, 7,5 hp</t>
+          <t>`Logik och matematik` (7,5hp); rad: - Logik och matematik, 7,5hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DBIMA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DDCMA</t>
+          <t>DITMG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Datadrivet ledarskap eller Ledarskapets ekonomi` (7,5 hp); rad: - Datadrivet ledarskap eller Ledarskapets ekonomi, 7,5 hp</t>
+          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DDCMA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DITMG</t>
+          <t>DSVPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Logik och matematik` (7,5hp); rad: - Logik och matematik, 7,5hp</t>
+          <t>`Datakommunikation I` (7,5 hp); rad: - Datakommunikation I, 7,5 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DITMG</t>
+          <t>DSVPG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5hp</t>
+          <t>`Data Storage &amp; Management Technologies` (7,5 hp); rad: - Data Storage &amp; Management Technologies, 7,5 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Datakommunikation I` (7,5 hp); rad: - Datakommunikation I, 7,5 hp</t>
+          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Data Storage &amp; Management Technologies` (7,5 hp); rad: - Data Storage &amp; Management Technologies, 7,5 hp</t>
+          <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`); rad: - [[GIK2JX|Webbaserade geografiska informationssystem]], 7,5 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DSVPG</t>
+          <t>KGDWG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KGDWG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DSVPG</t>
+          <t>TATPG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`); rad: - [[GIK2JX|Webbaserade geografiska informationssystem]], 7,5 hp</t>
+          <t>`Forskningsmetodik för ingenjörer` (7,5hp); rad: - Forskningsmetodik för ingenjörer, 7,5hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KGDWG</t>
+          <t>TATPG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5 hp</t>
+          <t>`Examensarbete i assisterande teknik med inriktning mot maskinteknik` (15 hp); rad: - Examensarbete i assisterande teknik med inriktning mot maskinteknik, 15 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KGDWG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Forskningsmetodik för ingenjörer` (7,5hp); rad: - Forskningsmetodik för ingenjörer, 7,5hp</t>
+          <t>`Finita elementmetoden i praktiken` (7,5 hp); rad: - Finita elementmetoden i praktiken, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TATPG</t>
+          <t>TBTCG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Examensarbete i assisterande teknik med inriktning mot maskinteknik` (15 hp); rad: - Examensarbete i assisterande teknik med inriktning mot maskinteknik, 15 hp</t>
+          <t>Programtext `Husbyggnadsprojekt I – Små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – Små byggnader och bostadsområden]], 15 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TATPG</t>
+          <t>TBTCG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden i praktiken` (7,5 hp); rad: - Finita elementmetoden i praktiken, 7,5 hp</t>
+          <t>Programtext `Husbyggnadsprojekt III – Byggkonstruktionsprojekt` ≠ kursplanens namn `Husbyggnadsprojekt III - Byggkonstruktionsprojekt` (kurskod `GBY3AX`); rad: - [[GBY3AX|Husbyggnadsprojekt III – Byggkonstruktionsprojekt]], 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TBTCG</t>
+          <t>TBTFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt I – Små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – Små byggnader och bostadsområden]], 15 hp</t>
+          <t>Programtext `Husbyggnadsprojekt I – små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – små byggnader och bostadsområden]], 15 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTFG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TBTCG</t>
+          <t>TBYSG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt III – Byggkonstruktionsprojekt` ≠ kursplanens namn `Husbyggnadsprojekt III - Byggkonstruktionsprojekt` (kurskod `GBY3AX`); rad: - [[GBY3AX|Husbyggnadsprojekt III – Byggkonstruktionsprojekt]], 7,5 hp</t>
+          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp); rad: - Fysisk planering III – genomförande och planeringsjuridik, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TBTFG</t>
+          <t>TBYSG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TBYSG</t>
+          <t>TEKHG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp); rad: - Fysisk planering III – genomförande och planeringsjuridik, 7,5 hp</t>
+          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TBYSG</t>
+          <t>TEKHG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt I – små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – små byggnader och bostadsområden]], 15 hp</t>
+          <t>Programtext `Industriell ekonomi – organisation och ledarskap` ≠ kursplanens namn `Industriell ekonomi - organisation och ledarskap` (kurskod `GIE26M`); rad: - [[GIE26M|Industriell ekonomi – organisation och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
+          <t>Programtext `Industriell ekonomi – underhåll och kvalitet` ≠ kursplanens namn `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`); rad: - [[GIE26N|Industriell ekonomi – underhåll och kvalitet]], 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TEKHG</t>
+          <t>THIHG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – organisation och ledarskap` ≠ kursplanens namn `Industriell ekonomi - organisation och ledarskap` (kurskod `GIE26M`); rad: - [[GIE26M|Industriell ekonomi – organisation och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TEKHG</t>
+          <t>THIHG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – underhåll och kvalitet` ≠ kursplanens namn `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`); rad: - [[GIE26N|Industriell ekonomi – underhåll och kvalitet]], 7,5 hp</t>
+          <t>Programtext `Utvecklingsprojekt, tillverkning av en solfångare` ≠ kursplanens namn `Utvecklingsprojekt, tillverkning av en solfångare` (kurskod `GEG2JP`); rad: - [[GEG2JP|Utvecklingsprojekt, tillverkning av en solfångare]], 7,5 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>THIHG</t>
+          <t>TMIEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
+          <t>Programtext `Byggnaders energiprestanda – simulering och analys` ≠ kursplanens namn `Byggnaders energiprestanda - simulering och analys` (kurskod `ABY22W`); rad: - [[ABY22W|Byggnaders energiprestanda – simulering och analys]], 5.0 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMIEA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>THIHG</t>
+          <t>TMSSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Programtext `Utvecklingsprojekt, tillverkning av en solfångare` ≠ kursplanens namn `Utvecklingsprojekt, tillverkning av en solfångare` (kurskod `GEG2JP`); rad: - [[GEG2JP|Utvecklingsprojekt, tillverkning av en solfångare]], 7,5 hp</t>
+          <t>`Solenergiteknikpraktik (7,5 eller` (15 hp); rad: - Solenergiteknikpraktik (7,5 eller, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TMIEA</t>
+          <t>TMSSA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Byggnaders energiprestanda – simulering och analys` ≠ kursplanens namn `Byggnaders energiprestanda - simulering och analys` (kurskod `ABY22W`); rad: - [[ABY22W|Byggnaders energiprestanda – simulering och analys]], 5.0 hp</t>
+          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMIEA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Solenergiteknikpraktik (7,5 eller` (15 hp); rad: - Solenergiteknikpraktik (7,5 eller, 15 hp</t>
+          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
+          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TMSSA</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
+          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TMSSA</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
+          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TPOKG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
+          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
+          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
+          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TPTAG</t>
+          <t>TSETA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,71 +1324,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
+          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>`CAM / CNC` (7,5 hp); rad: - CAM / CNC, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TSETA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E35"/>
+  <autoFilter ref="A1:E33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1454,10 +1400,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Solenergiteknikpraktik (7,5 eller` (15 hp); rad: - Solenergiteknikpraktik (7,5 eller, 15 hp</t>
+          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
+          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
+          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TMSSA</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
+          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TPOKG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
+          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
+          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
+          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
+          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TPTAG</t>
+          <t>TSETA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,49 +1292,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
+          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TSETA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E33"/>
+  <autoFilter ref="A1:E32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1398,8 +1371,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,7 +985,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>THIHG</t>
+          <t>TMIEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Programtext `Utvecklingsprojekt, tillverkning av en solfångare` ≠ kursplanens namn `Utvecklingsprojekt, tillverkning av en solfångare` (kurskod `GEG2JP`); rad: - [[GEG2JP|Utvecklingsprojekt, tillverkning av en solfångare]], 7,5 hp</t>
+          <t>Programtext `Byggnaders energiprestanda – simulering och analys` ≠ kursplanens namn `Byggnaders energiprestanda - simulering och analys` (kurskod `ABY22W`); rad: - [[ABY22W|Byggnaders energiprestanda – simulering och analys]], 5.0 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMIEA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TMIEA</t>
+          <t>TMSSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Programtext `Byggnaders energiprestanda – simulering och analys` ≠ kursplanens namn `Byggnaders energiprestanda - simulering och analys` (kurskod `ABY22W`); rad: - [[ABY22W|Byggnaders energiprestanda – simulering och analys]], 5.0 hp</t>
+          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMIEA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
+          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
+          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TMSSA</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
+          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TPOKG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
+          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
+          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
+          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
+          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TPTAG</t>
+          <t>TSETA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,49 +1265,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
+          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TSETA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1369,8 +1342,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Logik och matematik` (7,5hp); rad: - Logik och matematik, 7,5hp</t>
+          <t>`Logik och matematik` (7,5hp); rad: - Logik och matematik, 7,5hp — sannolikt avses `Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Datakommunikation I` (7,5 hp); rad: - Datakommunikation I, 7,5 hp</t>
+          <t>`Datakommunikation I` (7,5 hp); rad: - Datakommunikation I, 7,5 hp — sannolikt avses `Datakommunikation 1` (kurskod `GDT2JM`)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Data Storage &amp; Management Technologies` (7,5 hp); rad: - Data Storage &amp; Management Technologies, 7,5 hp</t>
+          <t>`Data Storage &amp; Management Technologies` (7,5 hp); rad: - Data Storage &amp; Management Technologies, 7,5 hp — sannolikt avses `Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden i praktiken` (7,5 hp); rad: - Finita elementmetoden i praktiken, 7,5 hp</t>
+          <t>`Finita elementmetoden i praktiken` (7,5 hp); rad: - Finita elementmetoden i praktiken, 7,5 hp — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TBTCG</t>
+          <t>TBYSG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt I – Små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – Små byggnader och bostadsområden]], 15 hp</t>
+          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp); rad: - Fysisk planering III – genomförande och planeringsjuridik, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TBTCG</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt III – Byggkonstruktionsprojekt` ≠ kursplanens namn `Husbyggnadsprojekt III - Byggkonstruktionsprojekt` (kurskod `GBY3AX`); rad: - [[GBY3AX|Husbyggnadsprojekt III – Byggkonstruktionsprojekt]], 7,5 hp</t>
+          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTCG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TBTFG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt I – små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – små byggnader och bostadsområden]], 15 hp</t>
+          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp — sannolikt avses `3D-CAD – grundkurs` (kurskod `GMT338`)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBTFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TBYSG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp); rad: - Fysisk planering III – genomförande och planeringsjuridik, 7,5 hp</t>
+          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TBYSG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Programtext `Husbyggnadsprojekt I – små byggnader och bostadsområden` ≠ kursplanens namn `Husbyggnadsprojekt I - Små byggnader och bostadsområden` (kurskod `GBY2J2`); rad: - [[GBY2J2|Husbyggnadsprojekt I – små byggnader och bostadsområden]], 15 hp</t>
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp — sannolikt avses `Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TEKHG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
+          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp — sannolikt avses `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TEKHG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – organisation och ledarskap` ≠ kursplanens namn `Industriell ekonomi - organisation och ledarskap` (kurskod `GIE26M`); rad: - [[GIE26M|Industriell ekonomi – organisation och ledarskap]], 7,5 hp</t>
+          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TEKHG</t>
+          <t>TSETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,346 +941,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Programtext `Industriell ekonomi – underhåll och kvalitet` ≠ kursplanens namn `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`); rad: - [[GIE26N|Industriell ekonomi – underhåll och kvalitet]], 7,5 hp</t>
+          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp — sannolikt avses `Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TEKHG</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>THIHG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Programtext `Industriell ekonomi – grundläggande kurs` ≠ kursplanens namn `Industriell ekonomi - grundläggande kurs` (kurskod `GIE26P`); rad: - [[GIE26P|Industriell ekonomi – grundläggande kurs]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=THIHG</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TMIEA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Programtext `Byggnaders energiprestanda – simulering och analys` ≠ kursplanens namn `Byggnaders energiprestanda - simulering och analys` (kurskod `ABY22W`); rad: - [[ABY22W|Byggnaders energiprestanda – simulering och analys]], 5.0 hp</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMIEA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TMSSA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Programtext `Projektkurs 1 – dataanalys för solenergisystem` ≠ kursplanens namn `Projektkurs 1 - dataanalys för solenergisystem` (kurskod `AEG2AK`); rad: - [[AEG2AK|Projektkurs 1 – dataanalys för solenergisystem]], 5 hp</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TMSSA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Programtext `Projektkurs 2 – mätsystem` ≠ kursplanens namn `Projektkurs 2 - mätsystem` (kurskod `AEG2AU`); rad: - [[AEG2AU|Projektkurs 2 – mätsystem]], 5 hp</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TMSSA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Programtext `Projektkurs 3 – grupprojekt och kommunikation` ≠ kursplanens namn `Projektkurs 3 - grupprojekt och kommunikation` (kurskod `AEG2B5`); rad: - [[AEG2B5|Projektkurs 3 – grupprojekt och kommunikation]], 5 hp</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TMSSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TPOKG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TSETA</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1318,30 +994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Logik och matematik` (7,5hp); rad: - Logik och matematik, 7,5hp — sannolikt avses `Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
+          <t>`Logik och matematik` (7,5hp) — sannolikt avses `Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5hp</t>
+          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Datakommunikation I` (7,5 hp); rad: - Datakommunikation I, 7,5 hp — sannolikt avses `Datakommunikation 1` (kurskod `GDT2JM`)</t>
+          <t>`Datakommunikation I` (7,5 hp) — sannolikt avses `Datakommunikation 1` (kurskod `GDT2JM`)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Data Storage &amp; Management Technologies` (7,5 hp); rad: - Data Storage &amp; Management Technologies, 7,5 hp — sannolikt avses `Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
+          <t>`Data Storage &amp; Management Technologies` (7,5 hp) — sannolikt avses `Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5 hp</t>
+          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`); rad: - [[GIK2JX|Webbaserade geografiska informationssystem]], 7,5 hp</t>
+          <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`); rad: - [[GIK2XZ|System- och verksamhetsutveckling]], 7,5 hp</t>
+          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Forskningsmetodik för ingenjörer` (7,5hp); rad: - Forskningsmetodik för ingenjörer, 7,5hp</t>
+          <t>`Finita elementmetoden i praktiken` (7,5 hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TATPG</t>
+          <t>TBYSG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Examensarbete i assisterande teknik med inriktning mot maskinteknik` (15 hp); rad: - Examensarbete i assisterande teknik med inriktning mot maskinteknik, 15 hp</t>
+          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TATPG</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden i praktiken` (7,5 hp); rad: - Finita elementmetoden i praktiken, 7,5 hp — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
+          <t>`Finita elementmetoden` (7,5hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TBYSG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp); rad: - Fysisk planering III – genomförande och planeringsjuridik, 7,5 hp</t>
+          <t>`3D CAD grundkurs` (7,5 hp) — sannolikt avses `3D-CAD – grundkurs` (kurskod `GMT338`)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TPOKG</t>
+          <t>TPTAG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden` (7,5hp); rad: - Finita elementmetoden, 7,5hp — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
+          <t>`Additiv tillverkning` (7,5 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`3D CAD grundkurs` (7,5 hp); rad: - 3D CAD grundkurs, 7,5 hp — sannolikt avses `3D-CAD – grundkurs` (kurskod `GMT338`)</t>
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp) — sannolikt avses `Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp); rad: - Additiv tillverkning, 7,5 hp</t>
+          <t>`Underhåll och kvalitet` (7,5 hp) — sannolikt avses `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp); rad: - Examensarbete för högskoleexamen inom maskinteknik, 7,5 hp — sannolikt avses `Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
+          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TPTAG</t>
+          <t>TSETA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,71 +892,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Underhåll och kvalitet` (7,5 hp); rad: - Underhåll och kvalitet, 7,5 hp — sannolikt avses `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
+          <t>`Design av PV hybrid system` (7,5 hp) — sannolikt avses `Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TPTAG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`); rad: - [[GMT34P|CAM / CNC]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TSETA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>`Design av PV hybrid system` (7,5 hp); rad: - Design av PV hybrid system, 7,5 hp — sannolikt avses `Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -990,10 +936,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp)</t>
+          <t>`Additiv tillverkning` (7,5 hp) — sannolikt avses `Additiv tillverkning (3D printing)` (kurskod `GMT34A`)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp)</t>
+          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp) — sannolikt avses `Fysisk planering III - genomförande och juridisk fördjupning` (kurskod `GSQ2PH`)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>`Logik och matematik` (7,5hp) — sannolikt avses `Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
@@ -536,15 +568,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2019-03-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Datakommunikation I` (7,5 hp) — sannolikt avses `Datakommunikation 1` (kurskod `GDT2JM`)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -563,15 +601,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2019-03-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Data Storage &amp; Management Technologies` (7,5 hp) — sannolikt avses `Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -590,15 +634,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2019-03-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -617,15 +667,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2019-03-05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -644,15 +700,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2021-10-08</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KGDWG</t>
         </is>
@@ -671,15 +733,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Finita elementmetoden i praktiken` (7,5 hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
@@ -698,15 +766,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>2019-12-18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2020-11-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp) — sannolikt avses `Fysisk planering III - genomförande och juridisk fördjupning` (kurskod `GSQ2PH`)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
@@ -725,15 +803,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>`Finita elementmetoden` (7,5hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -752,15 +840,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`3D CAD grundkurs` (7,5 hp) — sannolikt avses `3D-CAD – grundkurs` (kurskod `GMT338`)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -779,15 +873,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>`Additiv tillverkning` (7,5 hp) — sannolikt avses `Additiv tillverkning (3D printing)` (kurskod `GMT34A`)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -806,15 +906,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp) — sannolikt avses `Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -833,15 +939,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`Underhåll och kvalitet` (7,5 hp) — sannolikt avses `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -860,15 +972,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -887,55 +1005,65 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>`Design av PV hybrid system` (7,5 hp) — sannolikt avses `Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -509,10 +515,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Logik och matematik` (7,5hp) — sannolikt avses `Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>`Logik och matematik` (7,5hp)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`Logik och matematik för datavetenskap` (kurskod `GMI23G`)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
@@ -546,10 +557,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+          <t>`System- och verksamhetsutveckling`</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
@@ -579,10 +595,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Datakommunikation I` (7,5 hp) — sannolikt avses `Datakommunikation 1` (kurskod `GDT2JM`)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>`Datakommunikation I` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`Datakommunikation 1` (kurskod `GDT2JM`)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -612,10 +633,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Data Storage &amp; Management Technologies` (7,5 hp) — sannolikt avses `Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          <t>`Data Storage &amp; Management Technologies` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -645,10 +671,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>`System- och verksamhetsutveckling`</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -678,10 +709,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Programtext `Webbaserade geografiska informationssystem` ≠ kursplanens namn `Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          <t>`Webbaserade geografiska informationssystem`</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`Webbaserade geografiska informationssystem (GIS)` (kurskod `GIK2JX`)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
@@ -711,10 +747,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Programtext `System- och verksamhetsutveckling` ≠ kursplanens namn `System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          <t>`System- och verksamhetsutveckling`</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`System och verksamhetsutveckling` (kurskod `GIK2XZ`)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KGDWG</t>
         </is>
@@ -744,10 +785,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden i praktiken` (7,5 hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+          <t>`Finita elementmetoden i praktiken` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
@@ -781,10 +827,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp) — sannolikt avses `Fysisk planering III - genomförande och juridisk fördjupning` (kurskod `GSQ2PH`)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>`Fysisk planering III – genomförande och planeringsjuridik` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`Fysisk planering III - genomförande och juridisk fördjupning` (kurskod `GSQ2PH`)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TBYSG</t>
         </is>
@@ -818,10 +869,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Finita elementmetoden` (7,5hp) — sannolikt avses `Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+          <t>`Finita elementmetoden` (7,5hp)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`Finita element metoden i praktiken` (kurskod `GMT2QF`)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -851,10 +907,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`3D CAD grundkurs` (7,5 hp) — sannolikt avses `3D-CAD – grundkurs` (kurskod `GMT338`)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          <t>`3D CAD grundkurs` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`3D-CAD – grundkurs` (kurskod `GMT338`)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -884,10 +945,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Additiv tillverkning` (7,5 hp) — sannolikt avses `Additiv tillverkning (3D printing)` (kurskod `GMT34A`)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+          <t>`Additiv tillverkning` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`Additiv tillverkning (3D printing)` (kurskod `GMT34A`)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -917,10 +983,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp) — sannolikt avses `Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+          <t>`Examensarbete för högskoleexamen inom maskinteknik` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`Examensarbete för högskoleexamen i maskinteknik` (kurskod `GMT34W`)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -950,10 +1021,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Underhåll och kvalitet` (7,5 hp) — sannolikt avses `Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+          <t>`Underhåll och kvalitet` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`Industriell ekonomi - underhåll och kvalitet` (kurskod `GIE26N`)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -983,10 +1059,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Programtext `CAM / CNC` ≠ kursplanens namn `CAM/CNC` (kurskod `GMT34P`)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+          <t>`CAM / CNC`</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`CAM/CNC` (kurskod `GMT34P`)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPTAG</t>
         </is>
@@ -1020,50 +1101,55 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Design av PV hybrid system` (7,5 hp) — sannolikt avses `Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+          <t>`Design av PV hybrid system` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`Design av PV- och hybridsystem` (kurskod `AEG26X`)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TSETA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:H17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -590,7 +590,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Programkurser olänkade.xlsx
@@ -590,17 +590,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Datakommunikation I` (7,5 hp)</t>
+          <t>`Data Storage &amp; Management Technologies` (7,5 hp)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>`Datakommunikation 1` (kurskod `GDT2JM`)</t>
+          <t>`Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Data Storage &amp; Management Technologies` (7,5 hp)</t>
+          <t>`Datakommunikation I`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>`Data Storage and Management Technologies` (kurskod `GIK2NV`)</t>
+          <t>`Datakommunikation 1` (kurskod `GDT2JM`)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
